--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9573</v>
+        <v>9628</v>
       </c>
       <c r="K56" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6802,10 +6802,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6721</v>
+        <v>6743</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -10350,10 +10350,10 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>84829</v>
+        <v>84975</v>
       </c>
       <c r="K56" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -17459,10 +17459,10 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J56" t="n">
-        <v>11285</v>
+        <v>11322</v>
       </c>
       <c r="K56" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -21007,10 +21007,10 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J56" t="n">
-        <v>6907</v>
+        <v>6924</v>
       </c>
       <c r="K56" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -28103,10 +28103,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -32387,10 +32387,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J56" t="n">
-        <v>14743</v>
+        <v>14792</v>
       </c>
       <c r="K56" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -35935,10 +35935,10 @@
         <v>0.003607875476754974</v>
       </c>
       <c r="J56" t="n">
-        <v>2600</v>
+        <v>2618</v>
       </c>
       <c r="K56" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.007788857122934244</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>23814</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17435,16 +17435,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>149554</v>
+        <v>151492</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.06289799863543324</v>
+        <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.2420129184107413</v>
+        <v>-0.2517096612362369</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.007788857122934244</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>23814</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>144527</v>
+        <v>145876</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.007788857122934244</v>
+        <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9628</v>
+        <v>9630</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.4733440810367613</v>
+        <v>-0.4782143738517645</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>23814</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10353,7 +10353,7 @@
         <v>84975</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>9630</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -6787,16 +6787,16 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
-        <v>23814</v>
+        <v>24841</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>22325</v>
+        <v>24637</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10350,10 +10350,10 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>84975</v>
+        <v>85003</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -21010,7 +21010,7 @@
         <v>6924</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32390,7 +32390,7 @@
         <v>14792</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9630</v>
+        <v>9634</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>24841</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10350,10 +10350,10 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>85003</v>
+        <v>85027</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17459,7 +17459,7 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J56" t="n">
-        <v>11322</v>
+        <v>11332</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -21007,10 +21007,10 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J56" t="n">
-        <v>6924</v>
+        <v>6927</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32387,10 +32387,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J56" t="n">
-        <v>14792</v>
+        <v>14799</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>9634</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>24841</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10353,7 +10353,7 @@
         <v>85027</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17462,7 +17462,7 @@
         <v>11332</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32390,7 +32390,7 @@
         <v>14799</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>24841</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10353,7 +10353,7 @@
         <v>85027</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17462,7 +17462,7 @@
         <v>11332</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32390,7 +32390,7 @@
         <v>14799</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9634</v>
+        <v>9668</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>24841</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10353,7 +10353,7 @@
         <v>85027</v>
       </c>
       <c r="K56" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17462,7 +17462,7 @@
         <v>11332</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -21010,7 +21010,7 @@
         <v>6927</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32390,7 +32390,7 @@
         <v>14799</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9668</v>
+        <v>9682</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>24841</v>
@@ -6802,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6743</v>
+        <v>6744</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10350,10 +10350,10 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>85027</v>
+        <v>85066</v>
       </c>
       <c r="K56" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17459,10 +17459,10 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J56" t="n">
-        <v>11332</v>
+        <v>11351</v>
       </c>
       <c r="K56" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -21007,10 +21007,10 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J56" t="n">
-        <v>6927</v>
+        <v>6928</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32387,10 +32387,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J56" t="n">
-        <v>14799</v>
+        <v>14813</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.01719545359458894</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.03826936736143428</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>24841</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>145876</v>
+        <v>154310</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.01719545359458894</v>
+        <v>0.07600585733212467</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9682</v>
+        <v>9701</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.4782143738517645</v>
+        <v>-0.5067331994037976</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -6778,31 +6778,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>84783</v>
+        <v>85003</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.03826936736143428</v>
+        <v>0.04096353082367925</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
-        <v>24841</v>
+        <v>23472</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>24637</v>
+        <v>27649</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6744</v>
+        <v>6747</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.3604024391682295</v>
+        <v>-0.3620578097243627</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10350,10 +10350,10 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>85066</v>
+        <v>85216</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -17459,7 +17459,7 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J56" t="n">
-        <v>11351</v>
+        <v>11367</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -21007,7 +21007,7 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J56" t="n">
-        <v>6928</v>
+        <v>6937</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24555,7 +24555,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28103,7 +28103,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32387,7 +32387,7 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J56" t="n">
-        <v>14813</v>
+        <v>14827</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>
@@ -35935,7 +35935,7 @@
         <v>0.003607875476754974</v>
       </c>
       <c r="J56" t="n">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.07600585733212467</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.04096353082367925</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>23472</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -10350,10 +10350,10 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>85216</v>
+        <v>85244</v>
       </c>
       <c r="K56" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3239,7 +3239,7 @@
         <v>0.07600585733212467</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>9701</v>
+        <v>9700</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6787,7 +6787,7 @@
         <v>0.04096353082367925</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>23472</v>
@@ -10335,7 +10335,7 @@
         <v>0.05080470650341201</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>831889</v>
@@ -10350,7 +10350,7 @@
         <v>0.0490652389251815</v>
       </c>
       <c r="J56" t="n">
-        <v>85244</v>
+        <v>85243</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -13896,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17444,7 +17444,7 @@
         <v>0.07667159426881966</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>60022</v>
@@ -20992,7 +20992,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>83286</v>
@@ -24540,7 +24540,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.01947883940121974</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -32372,7 +32372,7 @@
         <v>0.1626084155521886</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>121213</v>
@@ -32387,7 +32387,7 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J56" t="n">
-        <v>14827</v>
+        <v>14826</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -35920,7 +35920,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10705,7 +10705,7 @@
         <v>0.02987454519706919</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.1524070811111242</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10705,7 +10705,7 @@
         <v>0.02987454519706919</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -32992,16 +32992,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>194902</v>
+        <v>203773</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.1524070811111242</v>
+        <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -33035,7 +33035,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.4912212291305374</v>
+        <v>-0.5133702698591079</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>38825</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -10720,7 +10720,7 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85243</v>
+        <v>85249</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -21488,7 +21488,7 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J64" t="n">
-        <v>6938</v>
+        <v>6940</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3553,7 +3553,7 @@
         <v>9702</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -10723,7 +10723,7 @@
         <v>85249</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -33019,7 +33019,7 @@
         <v>14826</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -10723,7 +10723,7 @@
         <v>85249</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -21491,7 +21491,7 @@
         <v>6940</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -33019,7 +33019,7 @@
         <v>14826</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3550,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9702</v>
+        <v>9711</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10696,16 +10696,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>923609</v>
+        <v>926319</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.02987454519706919</v>
+        <v>0.03289634340116211</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85249</v>
+        <v>85291</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1915799867692931</v>
+        <v>-0.1939450664403947</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -17903,7 +17903,7 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J64" t="n">
-        <v>11368</v>
+        <v>11400</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -21488,10 +21488,10 @@
         <v>0.3333653522885549</v>
       </c>
       <c r="J64" t="n">
-        <v>6940</v>
+        <v>6945</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -33016,10 +33016,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J64" t="n">
-        <v>14826</v>
+        <v>14839</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -36586,10 +36586,10 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="n">
-        <v>38825</v>
+        <v>38311</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -36598,7 +36598,7 @@
         <v>119</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.003607875476754974</v>
+        <v>-0.009638181630759716</v>
       </c>
       <c r="J64" t="n">
         <v>2622</v>
@@ -36635,7 +36635,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.1885014379622021</v>
+        <v>-0.177647671090294</v>
       </c>
       <c r="J65" t="n">
         <v>1051</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3553,7 +3553,7 @@
         <v>9711</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -7138,7 +7138,7 @@
         <v>6749</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -10723,7 +10723,7 @@
         <v>85291</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -17906,7 +17906,7 @@
         <v>11400</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -33019,7 +33019,7 @@
         <v>14839</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3553,7 +3553,7 @@
         <v>9711</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -7138,7 +7138,7 @@
         <v>6749</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -10723,7 +10723,7 @@
         <v>85291</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -17906,7 +17906,7 @@
         <v>11400</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
@@ -30433,7 +30433,7 @@
         <v>290</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -33019,7 +33019,7 @@
         <v>14839</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3550,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9711</v>
+        <v>9721</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10696,16 +10696,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>926319</v>
+        <v>927483</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.03289634340116211</v>
+        <v>0.03419426705782785</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85291</v>
+        <v>85310</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1939450664403947</v>
+        <v>-0.1949566730603149</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>9721</v>
+        <v>9726</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -7135,10 +7135,10 @@
         <v>1.104437674954718</v>
       </c>
       <c r="J64" t="n">
-        <v>6749</v>
+        <v>6753</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85310</v>
+        <v>85304</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -17903,10 +17903,10 @@
         <v>1.491209836527621</v>
       </c>
       <c r="J64" t="n">
-        <v>11400</v>
+        <v>11413</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -30430,10 +30430,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -33016,10 +33016,10 @@
         <v>0.3612787092903097</v>
       </c>
       <c r="J64" t="n">
-        <v>14839</v>
+        <v>14846</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>9726</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10705,7 +10705,7 @@
         <v>0.03419426705782785</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85304</v>
+        <v>85332</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -17906,7 +17906,7 @@
         <v>11413</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -33019,7 +33019,7 @@
         <v>14846</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,7 +3535,7 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>9726</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10705,7 +10705,7 @@
         <v>0.03419426705782785</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -10720,10 +10720,10 @@
         <v>0.04763604126127886</v>
       </c>
       <c r="J64" t="n">
-        <v>85332</v>
+        <v>85330</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -17906,7 +17906,7 @@
         <v>11413</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" t="n">
         <v>38311</v>

--- a/regionais/registroTLS.xlsx
+++ b/regionais/registroTLS.xlsx
@@ -3535,10 +3535,10 @@
         <v>0.07872533296143923</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>6845</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J65" t="n">
         <v>2771</v>
@@ -7120,7 +7120,7 @@
         <v>0.03848362308040023</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>23472</v>
@@ -10705,7 +10705,7 @@
         <v>0.03419426705782785</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>831889</v>
@@ -10723,7 +10723,7 @@
         <v>85330</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -14303,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -17888,7 +17888,7 @@
         <v>0.09210114851034797</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>60022</v>
@@ -21473,7 +21473,7 @@
         <v>0.006495849873691808</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>83286</v>
@@ -25058,7 +25058,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28643,7 +28643,7 @@
         <v>0.01628592483419307</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -30415,7 +30415,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -33001,7 +33001,7 @@
         <v>0.2048590991331906</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>121213</v>
@@ -33019,7 +33019,7 @@
         <v>14846</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -36586,7 +36586,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F64" t="n">
         <v>38311</v>
